--- a/excel/消费类样品.xlsx
+++ b/excel/消费类样品.xlsx
@@ -12578,7 +12578,7 @@
     <t>PCBA    F1885201</t>
   </si>
   <si>
-    <t>600188550011A</t>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>PCBA    F1841471</t>
@@ -13352,11 +13352,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="51">
     <font>
@@ -13528,22 +13528,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -13558,16 +13572,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13579,11 +13586,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13595,10 +13610,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13610,9 +13625,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -13628,7 +13642,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -13643,24 +13657,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13724,7 +13724,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13736,7 +13766,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13748,7 +13790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13760,7 +13802,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13772,7 +13850,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13784,79 +13874,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13868,43 +13886,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -14033,6 +14033,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -14043,17 +14058,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -14073,24 +14077,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -14106,17 +14092,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -14124,8 +14115,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -14137,10 +14137,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -14149,37 +14149,34 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -14188,94 +14185,97 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
